--- a/data/raw/fmcsa_carrier_compliance.xlsx
+++ b/data/raw/fmcsa_carrier_compliance.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/atharvabhalilkar/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/atharvabhalilkar/Documents/freight-analytics/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7D7C79F-CF53-5E42-9C01-943D08E69E81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5AD06CE-1971-A744-9640-6E4EFB18557E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="680" yWindow="660" windowWidth="28040" windowHeight="16940" xr2:uid="{246BB801-D6DE-1A4A-B473-22663E91EF72}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="62">
   <si>
     <t>carrier_name</t>
   </si>
@@ -1069,6 +1069,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7811301A-8298-5F4B-88FB-945019329858}">
   <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="30" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -1146,9 +1154,6 @@
       <c r="B4">
         <v>100003</v>
       </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
       <c r="D4" t="s">
         <v>11</v>
       </c>

--- a/data/raw/fmcsa_carrier_compliance.xlsx
+++ b/data/raw/fmcsa_carrier_compliance.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/atharvabhalilkar/Documents/freight-analytics/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5AD06CE-1971-A744-9640-6E4EFB18557E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CF3BF73-7B1E-164A-9885-1F0DA2D0545D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="660" windowWidth="28040" windowHeight="16940" xr2:uid="{246BB801-D6DE-1A4A-B473-22663E91EF72}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{246BB801-D6DE-1A4A-B473-22663E91EF72}"/>
   </bookViews>
   <sheets>
     <sheet name="fmcsa_carrier_compliance" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="62">
   <si>
     <t>carrier_name</t>
   </si>
@@ -1154,6 +1154,9 @@
       <c r="B4">
         <v>100003</v>
       </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
       <c r="D4" t="s">
         <v>11</v>
       </c>
